--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_966_Turkey_Marmara_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_966_Turkey_Marmara_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd6607ca3a5004823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9b8544cd121941b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re8072d0cd0074a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R03d89c507fea444d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1c5a43c47d5949d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdedaac5e22b64db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2ae9982494944936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R43b6c1d0a2454abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4ac8eec47f5a4d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc1d00795ca9240f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Radeadf7de31946ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R7b4578a2a39949f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ966CommercialTable" displayName="EEZ966CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ966CommercialTable" displayName="EEZ966CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ966FunctionalTable" displayName="EEZ966FunctionalTable" ref="A1:O24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O24"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ966FunctionalTable" displayName="EEZ966FunctionalTable" ref="A1:E24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E24"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ966ValidationTable" displayName="EEZ966ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ966ValidationTable" displayName="EEZ966ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6657,7 +6611,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R101443a770b045b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddc2191819e4467a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6667,20 +6621,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6688,660 +6632,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>25212.7004094679</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>25212.7004094679</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$90,A2,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3248024.999947031</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>3248024.999947031</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>998.9040540514001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.357592721132237</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2278.2045827373913</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>998.9040540514001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2279.0015690414707</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$90,A3,'Species'!$U$2:$U$90))</x:f>
-        <x:v>2276503.906505027</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.357592721132237</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2278.2045827373913</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2275707.7936548586</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>796.1128501682542</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0003498308756458</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00034983087564580156</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4673.1302365579995</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.309929043839165</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>204.140438746876</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4673.1302365579995</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>217.60463938125096</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$90,A4,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1016894.8199078235</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.309929043839165</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>204.140438746876</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>953974.8568122424</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>62919.96309558104</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0659555780178855</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.06595557801788554</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3675.5270442010997</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.132945903981762</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1358.1442646704768</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3675.5270442010997</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1813.5793304199763</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$90,A5,'Species'!$U$2:$U$90))</x:f>
-        <x:v>6665859.875762745</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.132945903981762</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1358.1442646704768</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4991895.9747229535</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1673963.9010397913</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.335336294970108</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.33533629497010803</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6710.9282293303</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0614533489491267</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>115.2002307378962</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6710.9282293303</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>119.40310108978528</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$90,A6,'Species'!$U$2:$U$90))</x:f>
-        <x:v>801305.6417730196</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0614533489491267</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>115.2002307378962</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>773100.4804843118</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>28205.16128870775</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0364831765090077</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03648317650900762</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>31761.2186981516</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.693648543353752</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>49.39108235147573</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>31761.2186981516</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>49.794388665553114</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$90,A7,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1581530.4683473937</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.693648543353752</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>49.39108235147573</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1568720.9683036364</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>12809.50004375726</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.008165569468743</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.008165569468743084</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>12642.908345257802</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.1611940831344847</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>144.94194441376285</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>12642.908345257802</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>209.21277688420687</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$90,A8,'Species'!$U$2:$U$90))</x:f>
-        <x:v>2645057.9628038974</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.1611940831344847</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>144.94194441376285</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1832487.7186066548</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>812570.2441972427</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4434246603382894</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.44342466033828937</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>38262.692464995394</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.769770165999227</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>588.5321144673763</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>38262.692464995394</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1290.5072557934948</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$90,A9,'Species'!$U$2:$U$90))</x:f>
-        <x:v>49378282.25227164</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.769770165999227</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>588.5321144673763</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>22518823.30163869</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>26859458.95063295</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.1927558820836963</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.1927558820836963</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>160.95946297300003</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7364705130117737</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>545.0928846427025</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>160.95946297300003</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>602.3235825075341</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$90,A10,'Species'!$U$2:$U$90))</x:f>
-        <x:v>96949.68037638615</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7364705130117737</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>545.0928846427025</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>87737.85798249286</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>9211.822393893293</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1049925608593205</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.10499256085932042</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4204.928016799</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9658938873263643</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>924.4722668329305</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4204.928016799</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>964.2191318114341</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$90,A11,'Species'!$U$2:$U$90))</x:f>
-        <x:v>4054472.041687507</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9658938873263643</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>924.4722668329305</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3887339.33555947</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>167132.70612803707</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0429941128625404</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.042994112862540505</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>6975.345279598199</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.48715856234074</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>3070.1427029677875</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>6975.345279598199</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>3098.56574021579</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$90,A12,'Species'!$U$2:$U$90))</x:f>
-        <x:v>21613565.90953891</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.48715856234074</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>3070.1427029677875</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>21415305.410839215</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>198260.49869969487</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0092578879869416</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.00925788798694165</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b304c37c42649a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5024dcb2d0d3444d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7351,20 +6866,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7372,1308 +6877,459 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>204.6280122533</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6593428889523465</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>456.3971134039412</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>204.6280122533</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>527.7740370569128</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$90,A2,'Species'!$U$2:$U$90))</x:f>
-        <x:v>107997.35212185557</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6593428889523465</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>456.3971134039412</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>93391.63411399243</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>14605.718007863135</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1563921452539916</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.15639214525399153</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>160.8064557486</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.3952136423317905</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2484.3549325929184</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>160.8064557486</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2500.8073482520017</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$90,A3,'Species'!$U$2:$U$90))</x:f>
-        <x:v>402145.9661824592</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.3952136423317905</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2484.3549325929184</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>399500.3115318193</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2645.6546506399172</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0066224094807226</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.006622409480722512</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>183.0344230218</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.53</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>3388.4415613920273</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>183.0344230218</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$90,A4,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>620201.4461324768</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.53</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>620201.4461324768</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2383.8797530370002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2887661149274825</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>194.4312708908291</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2383.8797530370002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>231.55899958539536</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$90,A5,'Species'!$U$2:$U$90))</x:f>
-        <x:v>552008.8107451271</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2887661149274825</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>194.4312708908291</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>463500.77003389975</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>88508.0407112274</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1909555418964117</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.19095554189641162</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3615.6574450677</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.1482284361720225</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1406.7872908430825</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3615.6574450677</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1840.9238886285523</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$90,A6,'Species'!$U$2:$U$90))</x:f>
-        <x:v>6656150.163722807</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.1482284361720225</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1406.7872908430825</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5086460.94176341</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1569689.2219593963</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3086014499926948</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3086014499926948</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>11146.764426432399</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.529268498034169</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>3382.739058861948</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>11146.764426432399</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>3383.006746620823</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$90,A7,'Species'!$U$2:$U$90))</x:f>
-        <x:v>37709579.25761379</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.529268498034169</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>3382.739058861948</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>37706595.405225776</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2983.8523880168796</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000791334342427</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00007913343424273585</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>322.3947373865</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>322.3947373865</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$90,A8,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>223042.6641852578</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>223042.6641852578</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>93.1678006977</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.43</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2691.534803926914</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>93.1678006977</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2691.534803926914</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$90,A9,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>250764.37818318576</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.43</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2691.534803926914</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>250764.37818318576</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>3436.1042343893</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9992593991435057</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>998.2961566998821</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>3436.1042343893</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1033.0745084007854</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$90,A10,'Species'!$U$2:$U$90))</x:f>
-        <x:v>3549751.6927555827</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9992593991435057</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>998.2961566998821</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3430249.651211029</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>119502.04154455382</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0348377096991657</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03483770969916558</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>790.9956722347</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.307615871112486</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>203.05602073451027</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>790.9956722347</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>261.7221654625911</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$90,A11,'Species'!$U$2:$U$90))</x:f>
-        <x:v>207021.1002088036</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.307615871112486</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>203.05602073451027</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>160616.43362219713</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>46404.66658660647</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2889160563467608</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.2889160563467608</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>89.3600787192</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.6643876626564316</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>461.729542578156</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>89.3600787192</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>624.210763102163</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$90,A12,'Species'!$U$2:$U$90))</x:f>
-        <x:v>55779.52292818119</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.6643876626564316</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>461.729542578156</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>41260.18827176423</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>14519.334656416962</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.351896955990214</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.35189695599021403</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3876.6066247992003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.636737263825105</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>433.24869558580895</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3876.6066247992003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>860.0829450532574</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$90,A13,'Species'!$U$2:$U$90))</x:f>
-        <x:v>3334203.242670264</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.636737263825105</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>433.24869558580895</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1679534.763493559</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1654668.479176705</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.9851945402635607</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.9851945402635607</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>10079.546611283</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.296520756676868</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>197.93416196594802</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>10079.546611283</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>210.45157578153817</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$90,A14,'Species'!$U$2:$U$90))</x:f>
-        <x:v>2121256.4675079705</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.296520756676868</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>197.93416196594802</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1995086.6115010118</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>126169.85600695875</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0632402900604072</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.06324029006040711</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>23011.4201016468</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.9593498229114643</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>910.6465003295576</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>23011.4201016468</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1316.5513095369618</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$90,A15,'Species'!$U$2:$U$90))</x:f>
-        <x:v>30295715.26912826</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.9593498229114643</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>910.6465003295576</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>20955269.183177892</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>9340446.085950367</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4457325746714114</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.4457325746714115</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>3665.0387665621997</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>3665.0387665621997</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$90,A16,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>124187.69680732318</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>124187.69680732318</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>33077.7183563733</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.6662748447511833</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>46.37403065332863</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>33077.7183563733</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>48.219755506461794</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$90,A17,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1594999.4918559238</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.6662748447511833</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>46.37403065332863</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1533947.1250006265</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>61052.36685529724</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0398008287640763</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0398008287640764</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>3882.1345643233</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.3104003591904534</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>204.3621011294416</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>3882.1345643233</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>208.61557122252668</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$90,A18,'Species'!$U$2:$U$90))</x:f>
-        <x:v>809873.7196990199</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.3104003591904534</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>204.3621011294416</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>793361.176432339</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>16512.543266680907</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0208133996938646</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.020813399693864604</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>326.0043594702</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.6078147165168164</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>405.3355698407969</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>326.0043594702</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>412.1747781909199</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$90,A19,'Species'!$U$2:$U$90))</x:f>
-        <x:v>134370.7745539026</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.6078147165168164</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>405.3355698407969</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>132141.16281643749</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>2229.6117374651076</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.016872953816536</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.016872953816535953</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>2490.3972114721996</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.040732452016628</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>109.83290031936994</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>2490.3972114721996</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>128.8663718351831</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$90,A20,'Species'!$U$2:$U$90))</x:f>
-        <x:v>320928.45307087956</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.040732452016628</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>109.83290031936994</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>273527.54868326295</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>47400.90438761661</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.173294809300929</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.17329480930092894</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>31936.5785660917</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0988563096891757</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>125.56144634062959</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>31936.5785660917</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>125.78028078720534</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$90,A21,'Species'!$U$2:$U$90))</x:f>
-        <x:v>4016991.819425658</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0988563096891757</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>125.56144634062959</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>4010002.995929624</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>6988.823496033903</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0017428474500214</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.001742847450021346</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>0.705396217</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>0.705396217</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$90,A22,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>90.87263603162825</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>90.87263603162825</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>59.8695991334</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.21</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>162.18100973589299</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>59.8695991334</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>162.18100973589299</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$90,A23,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>9709.712039937956</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.21</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>162.18100973589299</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>9709.712039937956</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>446.42904502320005</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.8000000000000003</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>630.9573444801937</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>446.42904502320005</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$90,A24,'Species'!$U$2:$U$90))</x:f>
-        <x:v>281677.6847466668</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.8000000000000003</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>630.9573444801937</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>281677.6847466671</x:v>
       </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>-2.9103830456733704e-10</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>-1.0332316698395494e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G24">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O24">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5165c3c78e24c02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cf667dfbf504fc9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8848,7 +7504,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8947,7 +7603,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>93378447.55892137</x:v>
+        <x:v>63553118.69855156</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8961,7 +7617,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>93378447.55892137</x:v>
+        <x:v>80264120.35753952</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8975,7 +7631,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-29825328.86036981</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8989,7 +7645,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-13114327.201381847</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9000,9 +7656,9 @@
         <x:v>EEZ_966</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9014,47 +7670,19 @@
         <x:v>EEZ_966</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_966</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_966</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdde4defd70dc483b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd474ca4820844644"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9101,7 +7729,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
